--- a/ACTIVE_JOB_DTSX_ANTIPATTERN_PRIORITY.xlsx
+++ b/ACTIVE_JOB_DTSX_ANTIPATTERN_PRIORITY.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sql\ssis_toolkit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA8FC39-0FAC-4B52-8832-01FBD288CD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3799D1F1-0F66-47B4-9545-23D521D087AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{1CDF7E49-CB86-40EA-8CAE-FDF0B2973B2A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$V$95</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1444,6 +1447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03649AEE-4E0C-4CE5-91E5-BBA787E26121}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A2:V95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1539,7 +1543,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1607,7 +1611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1675,7 +1679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -1743,7 +1747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -1811,7 +1815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -1879,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -1947,7 +1951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -2015,7 +2019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -2083,7 +2087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -2151,7 +2155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2219,7 +2223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -2287,7 +2291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -2355,7 +2359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>73</v>
       </c>
@@ -2423,7 +2427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>78</v>
       </c>
@@ -2491,7 +2495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>83</v>
       </c>
@@ -2559,7 +2563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>87</v>
       </c>
@@ -2627,7 +2631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>91</v>
       </c>
@@ -2695,7 +2699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>94</v>
       </c>
@@ -2763,7 +2767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>99</v>
       </c>
@@ -2831,7 +2835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -2899,7 +2903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>99</v>
       </c>
@@ -2967,7 +2971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>108</v>
       </c>
@@ -3035,7 +3039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>111</v>
       </c>
@@ -3103,7 +3107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>116</v>
       </c>
@@ -3171,7 +3175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>121</v>
       </c>
@@ -3239,7 +3243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>125</v>
       </c>
@@ -3307,7 +3311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>129</v>
       </c>
@@ -3375,7 +3379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>132</v>
       </c>
@@ -3443,7 +3447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>136</v>
       </c>
@@ -3511,7 +3515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>141</v>
       </c>
@@ -3579,7 +3583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>145</v>
       </c>
@@ -3647,7 +3651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>149</v>
       </c>
@@ -3715,7 +3719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>154</v>
       </c>
@@ -3783,7 +3787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>160</v>
       </c>
@@ -3851,7 +3855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>164</v>
       </c>
@@ -3919,7 +3923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>94</v>
       </c>
@@ -3987,7 +3991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>171</v>
       </c>
@@ -4055,7 +4059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>175</v>
       </c>
@@ -4123,7 +4127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>108</v>
       </c>
@@ -4191,7 +4195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>175</v>
       </c>
@@ -4259,7 +4263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>184</v>
       </c>
@@ -4327,7 +4331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>189</v>
       </c>
@@ -4395,7 +4399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>192</v>
       </c>
@@ -4463,7 +4467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>197</v>
       </c>
@@ -4531,7 +4535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>201</v>
       </c>
@@ -4599,7 +4603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>205</v>
       </c>
@@ -4667,7 +4671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>164</v>
       </c>
@@ -4735,7 +4739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>99</v>
       </c>
@@ -4803,7 +4807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>205</v>
       </c>
@@ -4871,7 +4875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>99</v>
       </c>
@@ -4939,7 +4943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>216</v>
       </c>
@@ -5007,7 +5011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>192</v>
       </c>
@@ -5075,7 +5079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>223</v>
       </c>
@@ -5143,7 +5147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>227</v>
       </c>
@@ -5211,7 +5215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>231</v>
       </c>
@@ -5347,7 +5351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>192</v>
       </c>
@@ -5415,7 +5419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>241</v>
       </c>
@@ -5483,7 +5487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>116</v>
       </c>
@@ -5551,7 +5555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>246</v>
       </c>
@@ -5619,7 +5623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>46</v>
       </c>
@@ -5687,7 +5691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>231</v>
       </c>
@@ -5755,7 +5759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>136</v>
       </c>
@@ -5823,7 +5827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>256</v>
       </c>
@@ -5891,7 +5895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>37</v>
       </c>
@@ -5959,7 +5963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>264</v>
       </c>
@@ -6027,7 +6031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>269</v>
       </c>
@@ -6095,7 +6099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>164</v>
       </c>
@@ -6163,7 +6167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>256</v>
       </c>
@@ -6231,7 +6235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>277</v>
       </c>
@@ -6299,7 +6303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>256</v>
       </c>
@@ -6367,7 +6371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>189</v>
       </c>
@@ -6435,7 +6439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>256</v>
       </c>
@@ -6503,7 +6507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>264</v>
       </c>
@@ -6571,7 +6575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>287</v>
       </c>
@@ -6639,7 +6643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>231</v>
       </c>
@@ -6707,7 +6711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>164</v>
       </c>
@@ -6775,7 +6779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>164</v>
       </c>
@@ -6843,7 +6847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>298</v>
       </c>
@@ -6911,7 +6915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>164</v>
       </c>
@@ -6979,7 +6983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>305</v>
       </c>
@@ -7047,7 +7051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>164</v>
       </c>
@@ -7115,7 +7119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>149</v>
       </c>
@@ -7183,7 +7187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>164</v>
       </c>
@@ -7251,7 +7255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>315</v>
       </c>
@@ -7319,7 +7323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>319</v>
       </c>
@@ -7387,7 +7391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>129</v>
       </c>
@@ -7455,7 +7459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>326</v>
       </c>
@@ -7523,7 +7527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>305</v>
       </c>
@@ -7591,7 +7595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>231</v>
       </c>
@@ -7659,7 +7663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>78</v>
       </c>
@@ -7727,7 +7731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>336</v>
       </c>
@@ -7795,7 +7799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>326</v>
       </c>
@@ -7864,6 +7868,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:V95" xr:uid="{03649AEE-4E0C-4CE5-91E5-BBA787E26121}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="DWH_GRADING_TBS"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>